--- a/Jacobs_etal_2018/Jacobs_etal_2018_Table5_snapshot.xlsx
+++ b/Jacobs_etal_2018/Jacobs_etal_2018_Table5_snapshot.xlsx
@@ -4297,13 +4297,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5742AEAB-EDD3-41E6-9556-152761C41BBE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF2A06B5-0926-4EB6-B1CF-81ED03E38B8F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99539251-E297-4342-9625-1C3461C132B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{222DD37E-49F8-4CBE-9F20-EC9950890C2C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBD27AC1-28E2-4CB3-8B59-634B90288578}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA128E22-5345-47A9-BED3-56957CF0A447}"/>
 </file>
--- a/Jacobs_etal_2018/Jacobs_etal_2018_Table5_snapshot.xlsx
+++ b/Jacobs_etal_2018/Jacobs_etal_2018_Table5_snapshot.xlsx
@@ -4297,13 +4297,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF2A06B5-0926-4EB6-B1CF-81ED03E38B8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07F77C0-E28B-4B6D-830B-08CD92E758BB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{222DD37E-49F8-4CBE-9F20-EC9950890C2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CCF932D-8273-4F4E-932C-6035F8DE05A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA128E22-5345-47A9-BED3-56957CF0A447}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{516846DB-AF23-4746-9994-AB93888E7375}"/>
 </file>